--- a/kpi-cards-template.xlsx
+++ b/kpi-cards-template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="51">
   <si>
     <t xml:space="preserve">N</t>
   </si>
@@ -34,31 +34,46 @@
     <t xml:space="preserve">Период</t>
   </si>
   <si>
+    <t xml:space="preserve">Формула расчёта</t>
+  </si>
+  <si>
     <t xml:space="preserve">Показатель</t>
   </si>
   <si>
+    <t xml:space="preserve">Тип</t>
+  </si>
+  <si>
     <t xml:space="preserve">Вес, %</t>
   </si>
   <si>
-    <t xml:space="preserve">Тип</t>
-  </si>
-  <si>
     <t xml:space="preserve">Глава дирекции</t>
   </si>
   <si>
     <t xml:space="preserve">Год</t>
   </si>
   <si>
-    <t xml:space="preserve">Средний KPI дирекции по качеству идей</t>
+    <t xml:space="preserve">Качество идей = 60% точность попадания + 40% опережение рынка (альфа)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Качество инвестидей</t>
   </si>
   <si>
     <t xml:space="preserve">KPI</t>
   </si>
   <si>
-    <t xml:space="preserve">Средний KPI дирекции по CSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инициативы (дорожная карта развития)</t>
+    <t xml:space="preserve">50% выполнение SLA + 50% индекс удовлетворённости; у аналитика — по его центру</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% задач дорожной карты, выполненных в срок (≤30 дн задержки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инициативы развития</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% вех проекта «Аналитика на базе ИИ», достигнутых в срок</t>
   </si>
   <si>
     <t xml:space="preserve">Внедрение ИИ</t>
@@ -67,12 +82,18 @@
     <t xml:space="preserve">Итого</t>
   </si>
   <si>
-    <t xml:space="preserve">Оценка руководителя (кэп 120%)</t>
+    <t xml:space="preserve">Множитель поверх итога, кэп 120%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка руководителя</t>
   </si>
   <si>
     <t xml:space="preserve">Коэффициент</t>
   </si>
   <si>
+    <t xml:space="preserve">Множитель от финансового результата дирекции</t>
+  </si>
+  <si>
     <t xml:space="preserve">Операционная прибыль</t>
   </si>
   <si>
@@ -82,64 +103,52 @@
     <t xml:space="preserve">Руководитель центра аналитики</t>
   </si>
   <si>
-    <t xml:space="preserve">Качество идей центра (точность 60% + альфа 40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSI центра</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инициативы</t>
-  </si>
-  <si>
     <t xml:space="preserve">Аналитик акций/облигаций</t>
   </si>
   <si>
-    <t xml:space="preserve">Точность попадания идей (60% качества)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Опережение рынка — альфа (40% качества)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSI по центру</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аналитическая гигиена — дисконт до 40%</t>
+    <t xml:space="preserve">Множитель ×(1−дисконт): отчёты 20%, конфликт 10%, first take 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитическая гигиена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дисконт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">до −40%</t>
   </si>
   <si>
     <t xml:space="preserve">Макроэкономист</t>
   </si>
   <si>
-    <t xml:space="preserve">Точность годовых прогнозов (инфляция, ставка ЦБ, ВВП)</t>
+    <t xml:space="preserve">Точность годовых прогнозов: инфляция, ставка ЦБ, ВВП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Качество прогнозов</t>
   </si>
   <si>
     <t xml:space="preserve">Стратег по классам активов</t>
   </si>
   <si>
+    <t xml:space="preserve">Доходность портфеля/стратегии за период</t>
+  </si>
+  <si>
     <t xml:space="preserve">Результат портфелей</t>
   </si>
   <si>
-    <t xml:space="preserve">Качество идей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Управляющий акции РФ</t>
   </si>
   <si>
     <t xml:space="preserve">Аналитик по продуктам БКС</t>
   </si>
   <si>
-    <t xml:space="preserve">Решение руководителя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA по качеству продукта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSI продуктовой дирекции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инициативы развития</t>
+    <t xml:space="preserve">Дискреционная оценка руководителя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка руководителя (KPI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% SLA по качеству продукта + 15% CSI продуктовой дирекции</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель продаж</t>
@@ -148,13 +157,16 @@
     <t xml:space="preserve">Директор по продукту</t>
   </si>
   <si>
+    <t xml:space="preserve">Продуктовая метрика</t>
+  </si>
+  <si>
     <t xml:space="preserve">Оборот по инвестидеям</t>
   </si>
   <si>
     <t xml:space="preserve">Заводы по инвестидеям</t>
   </si>
   <si>
-    <t xml:space="preserve">Количество уникальных пользователей</t>
+    <t xml:space="preserve">Кол-во уникальных пользователей</t>
   </si>
   <si>
     <t xml:space="preserve">CSI по аналитике и инвестидеям</t>
@@ -171,7 +183,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,29 +227,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="9.5"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9.5"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9.5"/>
-      <color rgb="FF666666"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,30 +237,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3A5F"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="FF34495E"/>
+        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6F9"/>
-        <bgColor rgb="FFFBFBFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFBFB"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3B0"/>
+        <fgColor rgb="FFFDECEF"/>
         <bgColor rgb="FFF4F6F9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -279,16 +264,31 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFC8CDD5"/>
+        <color rgb="FFB0B8C4"/>
       </left>
       <right style="thin">
-        <color rgb="FFC8CDD5"/>
+        <color rgb="FFB0B8C4"/>
       </right>
       <top style="thin">
-        <color rgb="FFC8CDD5"/>
+        <color rgb="FFB0B8C4"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC8CDD5"/>
+        <color rgb="FFB0B8C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFB0B8C4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B8C4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B8C4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7A8699"/>
       </bottom>
       <diagonal/>
     </border>
@@ -318,7 +318,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -327,44 +327,48 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -392,12 +396,12 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC8CDD5"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFB0B8C4"/>
+      <rgbColor rgb="FF7A8699"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFBFBFB"/>
       <rgbColor rgb="FFF4F6F9"/>
+      <rgbColor rgb="FFFDECEF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -413,7 +417,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFF3B0"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -424,16 +428,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3A5F"/>
+      <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF34495E"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -619,19 +623,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,6 +657,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -659,22 +667,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>40</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -683,13 +694,16 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -698,13 +712,16 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -713,13 +730,16 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -727,62 +747,72 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <f aca="false">SUM(F2:F5)</f>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9" t="n">
+        <f aca="false">SUM(H2:H5)</f>
         <v>100</v>
       </c>
-      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>40</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,13 +821,16 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -806,13 +839,16 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -821,13 +857,16 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -835,62 +874,72 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <f aca="false">SUM(F9:F12)</f>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9" t="n">
+        <f aca="false">SUM(H9:H12)</f>
         <v>100</v>
       </c>
-      <c r="G13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>45</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -899,13 +948,16 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -914,13 +966,16 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="5" t="n">
         <v>15</v>
       </c>
+      <c r="F18" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="G18" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -929,13 +984,16 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -943,62 +1001,72 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <f aca="false">SUM(F16:F19)</f>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="9" t="n">
+        <f aca="false">SUM(H16:H19)</f>
         <v>100</v>
       </c>
-      <c r="G20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1007,13 +1075,16 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1022,13 +1093,16 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1037,12 +1111,15 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1051,14 +1128,14 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>10</v>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9" t="n">
+        <f aca="false">SUM(H23:H26)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1066,75 +1143,93 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <f aca="false">SUM(F23:F27)</f>
-        <v>100</v>
-      </c>
-      <c r="G28" s="6"/>
+      <c r="E28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+      <c r="E30" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="2" t="n">
+      <c r="B31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,13 +1238,16 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1158,12 +1256,15 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="G34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1172,14 +1273,14 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>10</v>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="9" t="n">
+        <f aca="false">SUM(H31:H34)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1187,75 +1288,93 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <f aca="false">SUM(F32:F35)</f>
-        <v>100</v>
-      </c>
-      <c r="G36" s="6"/>
+      <c r="E36" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+      <c r="E38" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
       <c r="E40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,13 +1383,16 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1279,13 +1401,16 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1294,12 +1419,15 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="G43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1308,14 +1436,14 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>10</v>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="9" t="n">
+        <f aca="false">SUM(H39:H43)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,62 +1451,75 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <f aca="false">SUM(F40:F44)</f>
-        <v>100</v>
-      </c>
-      <c r="G45" s="6"/>
+      <c r="E45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1387,13 +1528,16 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1402,12 +1546,15 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G50" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1417,13 +1564,16 @@
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1431,14 +1581,14 @@
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>10</v>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="9" t="n">
+        <f aca="false">SUM(H47:H51)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1446,62 +1596,75 @@
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <f aca="false">SUM(F48:F52)</f>
-        <v>100</v>
-      </c>
-      <c r="G53" s="6"/>
+      <c r="E53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+      <c r="E54" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="2" t="n">
+      <c r="B55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
       <c r="E56" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,14 +1672,17 @@
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" s="11" t="n">
+      <c r="E57" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G57" s="11" t="s">
-        <v>10</v>
+      <c r="F57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1524,14 +1690,17 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" s="11" t="n">
+      <c r="E58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1539,14 +1708,14 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>10</v>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="8"/>
+      <c r="H59" s="9" t="n">
+        <f aca="false">SUM(H55:H58)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1555,40 +1724,56 @@
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <f aca="false">SUM(F56:F60)</f>
-        <v>100</v>
-      </c>
-      <c r="G61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9" t="s">
-        <v>16</v>
+      <c r="E61" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1596,35 +1781,32 @@
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>10</v>
+      <c r="E63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="8"/>
+      <c r="H64" s="9" t="n">
+        <f aca="false">SUM(H62:H63)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1633,40 +1815,56 @@
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>70</v>
+        <v>20</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <f aca="false">SUM(F64:F65)</f>
-        <v>100</v>
-      </c>
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9" t="s">
-        <v>16</v>
+      <c r="E66" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1674,35 +1872,35 @@
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F69" s="11" t="n">
+      <c r="E68" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="G69" s="11" t="s">
-        <v>10</v>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1710,14 +1908,17 @@
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" s="11" t="n">
+      <c r="E70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,14 +1926,14 @@
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>10</v>
+      <c r="E71" s="6"/>
+      <c r="F71" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="8"/>
+      <c r="H71" s="9" t="n">
+        <f aca="false">SUM(H67:H70)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1740,41 +1941,57 @@
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G72" s="11" t="s">
-        <v>10</v>
-      </c>
+      <c r="E72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <f aca="false">SUM(F69:F72)</f>
-        <v>100</v>
-      </c>
-      <c r="G73" s="6"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9" t="s">
-        <v>16</v>
+      <c r="E73" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1782,35 +1999,35 @@
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9" t="s">
+      <c r="E75" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="G76" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1819,13 +2036,16 @@
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,14 +2053,14 @@
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>10</v>
+      <c r="E78" s="6"/>
+      <c r="F78" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="8"/>
+      <c r="H78" s="9" t="n">
+        <f aca="false">SUM(H74:H77)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1849,54 +2069,31 @@
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <f aca="false">SUM(F76:F79)</f>
-        <v>100</v>
-      </c>
-      <c r="G80" s="6"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="E80" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -1912,38 +2109,38 @@
     <mergeCell ref="B16:B22"/>
     <mergeCell ref="C16:C22"/>
     <mergeCell ref="D16:D22"/>
-    <mergeCell ref="A23:A31"/>
-    <mergeCell ref="B23:B31"/>
-    <mergeCell ref="C23:C31"/>
-    <mergeCell ref="D23:D31"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="B32:B39"/>
-    <mergeCell ref="C32:C39"/>
-    <mergeCell ref="D32:D39"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="C40:C47"/>
-    <mergeCell ref="D40:D47"/>
-    <mergeCell ref="A48:A55"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="C48:C55"/>
-    <mergeCell ref="D48:D55"/>
-    <mergeCell ref="A56:A63"/>
-    <mergeCell ref="B56:B63"/>
-    <mergeCell ref="C56:C63"/>
-    <mergeCell ref="D56:D63"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="C64:C68"/>
-    <mergeCell ref="D64:D68"/>
-    <mergeCell ref="A69:A75"/>
-    <mergeCell ref="B69:B75"/>
-    <mergeCell ref="C69:C75"/>
-    <mergeCell ref="D69:D75"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="B76:B82"/>
-    <mergeCell ref="C76:C82"/>
-    <mergeCell ref="D76:D82"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="C23:C30"/>
+    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="B31:B38"/>
+    <mergeCell ref="C31:C38"/>
+    <mergeCell ref="D31:D38"/>
+    <mergeCell ref="A39:A46"/>
+    <mergeCell ref="B39:B46"/>
+    <mergeCell ref="C39:C46"/>
+    <mergeCell ref="D39:D46"/>
+    <mergeCell ref="A47:A54"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="C47:C54"/>
+    <mergeCell ref="D47:D54"/>
+    <mergeCell ref="A55:A61"/>
+    <mergeCell ref="B55:B61"/>
+    <mergeCell ref="C55:C61"/>
+    <mergeCell ref="D55:D61"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="D62:D66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="B67:B73"/>
+    <mergeCell ref="C67:C73"/>
+    <mergeCell ref="D67:D73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="B74:B80"/>
+    <mergeCell ref="C74:C80"/>
+    <mergeCell ref="D74:D80"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/kpi-cards-template.xlsx
+++ b/kpi-cards-template.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Карта KPI" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Методология" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="84">
   <si>
     <t xml:space="preserve">N</t>
   </si>
@@ -173,6 +174,107 @@
   </si>
   <si>
     <t xml:space="preserve">Группа выпуска (редакторы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Роли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Методология расчёта плана и факта (описание) + формула</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Статус</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Глава, рук. развития, рук. центра, аналитик акц/обл, стратег, управляющий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Качество = 60% точность попадания + 40% опережение рынка (альфа).
+ТОЧНОСТЬ: hit-rate = идеи в цель ÷ все оценённые идеи за период. Критерии: Buy ≥90% целевой, Sell ≤110%, Hold 90–110%. Замер на конец срока по цене закрытия, в полной доходности (с дивидендами). Незакрытые — аннуализация тренда к цели. Минимум 1 месяц фактического срока (кроме валюты). Источник: Bloomberg + внутренний трекинг.
+АЛЬФА: только Buy/Sell внутри года, от открытия до смены рекомендации или конца года; цены total return; сравнение с бенчмарком (РФ акции — MCFTR, US — S&amp;P 500 TR, облигации — уточняется); альфа идеи = доходность − бенчмарк (Sell — обратный знак), годовая; итог = среднее по идеям.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Готово</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Качество прогнозов (макро)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точность ключевых прогнозов на горизонте года: инфляция, ставка ЦБ, рост ВВП. Замер — факт против прогноза через год.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все роли с CSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSI = 50% выполнение SLA (доля выполненных обязательств) + 50% индекс удовлетворённости (опрос заказчиков, шкала 1–5, взвешенно по аллокации затрат). У аналитика CSI считается по его центру: акции РФ, акции Мир, облигации, макроэкономика, стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSI (аналитик по продуктам)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% = 15% выполнение SLA по качеству продукта + 15% CSI продуктовой дирекции.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все роли с компонентом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% задач дорожной карты 2026, выполненных в срок (допустимая задержка ≤30 дней).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% вех проекта «Аналитика на базе ИИ», достигнутых в срок.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стратег по классам активов, управляющий акции РФ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность портфеля/стратегии за период. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: абсолютная или против бенчмарка, какой бенчмарк, риск-поправка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уточнить</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитик по продуктам, рук. продаж, группа выпуска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дискреционная оценка руководителя по итогам периода. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: критерии/шкала.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оборот считается по сделкам, совершённым в МП. Сделка засчитывается, если после просмотра инвестидеи (больше 5 секунд нахождения на странице инвестидеи) была совершена сделка в течение последующих 24 часов. В расчёте не участвуют интрадейщики (более 14 сделок в день по тикеру). Учитываются все инвестидеи на любой срок и по всем направлениям. Инструмент для учёта — Tableau (tableau.mybroker.global.bcs).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фондирование (заводы) по инвестидеям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Считается завод новых средств после просмотра инвестидеи и совершение сделки по этой бумаге. Логика: просмотрел инвестидею (больше 5 секунд на странице) → пополнил счёт на сумму n → совершил сделку в течение 24 часов по данной инвестидее. Логика учёта аналогична показателю «Оборот по инвестидеям»: просмотры идеи от 5 секунд и выше, учитываются сделки в МП по инвестидеям с любым сроком, направлением и базовым активом. Инструмент для учёта (будет реализован) — Tableau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество уникальных ID_Client, совершивших хотя бы одну сделку в течение года после просмотра инвестидеи (окно атрибуции — 24 часа). Инструмент для учёта — Tableau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднее значение по 4 показателям из CSI «Самостоятельная торговля» по существующей методологии опросов VoC: CSI Отображение инвестидей в МП · CSI Качество идей · CSI Понятность идей · CSI Количество идей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитическая гигиена (дисконт)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитик акций/облигаций, макроэкономист</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Множитель поверх итога: бонус = KPI × (1 − дисконт). Дисконт до 40% (типично ~15%): отчёты вовремя −20% (≥90% зачёт, &lt;30% ноль), реакция на конфликт −10% (&lt;15 дн зачёт, &gt;45 дн ноль), первый взгляд −10% (время &lt;1ч/-2ч + охват &gt;75%/&lt;30%, среднее двух). Достижение линейно между порогами. Удерживается из квартальных бонусов, перераспределяется между аналитиками с чистой гигиеной.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка руководителя (коэффициент)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Все роли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Множитель поверх итога карты, кэп 120%. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: шкала и критерии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Операционная прибыль (коэффициент)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Множитель от финансового результата. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: чья прибыль (дирекция/блок/группа), шкала.</t>
   </si>
 </sst>
 </file>
@@ -183,7 +285,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,8 +329,32 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2E9E4F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,6 +376,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDECEF"/>
+        <bgColor rgb="FFF4F6F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFF4F6F9"/>
       </patternFill>
     </fill>
@@ -318,8 +456,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -335,7 +477,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -343,11 +485,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -359,16 +501,40 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -384,10 +550,10 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFF200"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -401,7 +567,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF4F6F9"/>
-      <rgbColor rgb="FFFDECEF"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -415,7 +581,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFDECEF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -431,7 +597,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF2E9E4F"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -626,1474 +792,1474 @@
   <dimension ref="A1:H80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="n">
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9" t="n">
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="n">
         <f aca="false">SUM(H2:H5)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="10" t="s">
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="G10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="G11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="G12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9" t="n">
+      <c r="G13" s="9"/>
+      <c r="H13" s="10" t="n">
         <f aca="false">SUM(H9:H12)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="10" t="s">
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="G16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="G17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="5" t="n">
+      <c r="G18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="5" t="n">
+      <c r="G19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9" t="n">
+      <c r="G20" s="9"/>
+      <c r="H20" s="10" t="n">
         <f aca="false">SUM(H16:H19)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="10" t="s">
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="2"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="G24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="G25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="5" t="n">
+      <c r="G26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="7" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9" t="n">
+      <c r="G27" s="9"/>
+      <c r="H27" s="10" t="n">
         <f aca="false">SUM(H23:H26)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="11" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="4" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="10" t="s">
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="G31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="4" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" s="5" t="n">
+      <c r="G32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="4" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="G33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="4" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="G34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="7" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9" t="n">
+      <c r="G35" s="9"/>
+      <c r="H35" s="10" t="n">
         <f aca="false">SUM(H31:H34)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="11" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="4" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="10" t="s">
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="2"/>
+      <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="G39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="4" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" s="5" t="n">
+      <c r="G40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="4" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="G41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="4" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42" s="5" t="n">
+      <c r="G42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="4" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H43" s="5" t="n">
+      <c r="G43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="7" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G44" s="8"/>
-      <c r="H44" s="9" t="n">
+      <c r="G44" s="9"/>
+      <c r="H44" s="10" t="n">
         <f aca="false">SUM(H39:H43)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="4" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="10" t="s">
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="2"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="5" t="n">
+      <c r="G47" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="4" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="5" t="n">
+      <c r="G48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="4" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49" s="5" t="n">
+      <c r="G49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="4" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50" s="5" t="n">
+      <c r="G50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="4" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="5" t="n">
+      <c r="G51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="7" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9" t="n">
+      <c r="G52" s="9"/>
+      <c r="H52" s="10" t="n">
         <f aca="false">SUM(H47:H51)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="4" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="10" t="s">
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="2"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" s="5" t="n">
+      <c r="G55" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="4" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" s="5" t="n">
+      <c r="G56" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="4" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H57" s="5" t="n">
+      <c r="G57" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="4" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H58" s="5" t="n">
+      <c r="G58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="7" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9" t="n">
+      <c r="G59" s="9"/>
+      <c r="H59" s="10" t="n">
         <f aca="false">SUM(H55:H58)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="4" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H60" s="5"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="10" t="s">
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H61" s="2"/>
+      <c r="H61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H62" s="5" t="n">
+      <c r="G62" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="4" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H63" s="5" t="n">
+      <c r="G63" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="6" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="7" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G64" s="8"/>
-      <c r="H64" s="9" t="n">
+      <c r="G64" s="9"/>
+      <c r="H64" s="10" t="n">
         <f aca="false">SUM(H62:H63)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="4" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="G65" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="5"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="10" t="s">
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="2"/>
+      <c r="H66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H67" s="5" t="n">
+      <c r="G67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="4" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H68" s="5" t="n">
+      <c r="G68" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="4" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H69" s="5" t="n">
+      <c r="G69" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="4" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" s="5" t="n">
+      <c r="G70" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="7" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="8"/>
-      <c r="H71" s="9" t="n">
+      <c r="G71" s="9"/>
+      <c r="H71" s="10" t="n">
         <f aca="false">SUM(H67:H70)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="4" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="10" t="s">
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="2"/>
+      <c r="H73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H74" s="5" t="n">
+      <c r="G74" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" s="6" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="4" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="5" t="n">
+      <c r="G75" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="4" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="5" t="n">
+      <c r="G76" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="4" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H77" s="5" t="n">
+      <c r="G77" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="7" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G78" s="8"/>
-      <c r="H78" s="9" t="n">
+      <c r="G78" s="9"/>
+      <c r="H78" s="10" t="n">
         <f aca="false">SUM(H74:H77)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="4" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H79" s="5"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="10" t="s">
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H80" s="2"/>
+      <c r="H80" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -2150,4 +2316,253 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/kpi-cards-template.xlsx
+++ b/kpi-cards-template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="83">
   <si>
     <t xml:space="preserve">N</t>
   </si>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">Оборот по инвестидеям</t>
   </si>
   <si>
-    <t xml:space="preserve">Заводы по инвестидеям</t>
+    <t xml:space="preserve">Фондирование по инвестидеям</t>
   </si>
   <si>
     <t xml:space="preserve">Кол-во уникальных пользователей</t>
@@ -239,9 +239,6 @@
   </si>
   <si>
     <t xml:space="preserve">Оборот считается по сделкам, совершённым в МП. Сделка засчитывается, если после просмотра инвестидеи (больше 5 секунд нахождения на странице инвестидеи) была совершена сделка в течение последующих 24 часов. В расчёте не участвуют интрадейщики (более 14 сделок в день по тикеру). Учитываются все инвестидеи на любой срок и по всем направлениям. Инструмент для учёта — Tableau (tableau.mybroker.global.bcs).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фондирование (заводы) по инвестидеям</t>
   </si>
   <si>
     <t xml:space="preserve">Считается завод новых средств после просмотра инвестидеи и совершение сделки по этой бумаге. Логика: просмотрел инвестидею (больше 5 секунд на странице) → пополнил счёт на сумму n → совершил сделку в течение 24 часов по данной инвестидее. Логика учёта аналогична показателю «Оборот по инвестидеям»: просмотры идеи от 5 секунд и выше, учитываются сделки в МП по инвестидеям с любым сроком, направлением и базовым активом. Инструмент для учёта (будет реализован) — Tableau.</t>
@@ -2326,13 +2323,13 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
         <v>5</v>
       </c>
@@ -2346,7 +2343,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
         <v>11</v>
       </c>
@@ -2360,7 +2357,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
         <v>57</v>
       </c>
@@ -2374,7 +2371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
         <v>14</v>
       </c>
@@ -2388,7 +2385,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
         <v>61</v>
       </c>
@@ -2402,7 +2399,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2416,7 +2413,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
         <v>18</v>
       </c>
@@ -2430,7 +2427,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
         <v>37</v>
       </c>
@@ -2444,7 +2441,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>41</v>
       </c>
@@ -2458,7 +2455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
         <v>46</v>
       </c>
@@ -2472,21 +2469,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
         <v>48</v>
       </c>
@@ -2494,13 +2491,13 @@
         <v>44</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>49</v>
       </c>
@@ -2508,49 +2505,49 @@
         <v>44</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>78</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>68</v>

--- a/kpi-cards-template.xlsx
+++ b/kpi-cards-template.xlsx
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Стратег по классам активов</t>
   </si>
   <si>
-    <t xml:space="preserve">Доходность портфеля/стратегии за период</t>
+    <t xml:space="preserve">Средневзвешенный доход клиентов стратегий автоследования ДИА (после комиссий), взвешенный на долю в активах стратегий</t>
   </si>
   <si>
     <t xml:space="preserve">Результат портфелей</t>
@@ -226,16 +226,18 @@
     <t xml:space="preserve">Стратег по классам активов, управляющий акции РФ</t>
   </si>
   <si>
-    <t xml:space="preserve">Доходность портфеля/стратегии за период. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: абсолютная или против бенчмарка, какой бенчмарк, риск-поправка.</t>
+    <t xml:space="preserve">Средневзвешенный доход клиентов стратегий автоследования ДИА (после комиссий), взвешенный на долю в активах каждой стратегии.
+Стратег по классам активов: «Формула дохода» + новые стратегии, запускаемые в течение года.
+Управляющий акции РФ: «ТВ Лонг», «ТВ Рыночный», «ТВ Нейтральный», «Парные идеи» + новые стратегии, запускаемые в течение года.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитик по продуктам, рук. продаж, группа выпуска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дискреционная оценка руководителя по итогам периода. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: критерии/шкала.</t>
   </si>
   <si>
     <t xml:space="preserve">Уточнить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аналитик по продуктам, рук. продаж, группа выпуска</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дискреционная оценка руководителя по итогам периода. ТРЕБУЕТ ДЕТАЛИЗАЦИИ: критерии/шкала.</t>
   </si>
   <si>
     <t xml:space="preserve">Оборот считается по сделкам, совершённым в МП. Сделка засчитывается, если после просмотра инвестидеи (больше 5 секунд нахождения на странице инвестидеи) была совершена сделка в течение последующих 24 часов. В расчёте не участвуют интрадейщики (более 14 сделок в день по тикеру). Учитываются все инвестидеи на любой срок и по всем направлениям. Инструмент для учёта — Tableau (tableau.mybroker.global.bcs).</t>
@@ -2437,8 +2439,8 @@
       <c r="C8" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>68</v>
+      <c r="D8" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2446,13 +2448,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2536,7 +2538,7 @@
         <v>80</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2550,7 +2552,7 @@
         <v>82</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
